--- a/interview_forms/044_remote_job_interview_form--interview_forms.xlsx
+++ b/interview_forms/044_remote_job_interview_form--interview_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'gmt'}</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'GMT'}</t>
+          <t>GMT</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'archived'}</t>
+          <t>archived</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Archived'}</t>
+          <t>Archived</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
